--- a/Capítulo02/Capítulo02/LOJA DE CARROS .xlsx
+++ b/Capítulo02/Capítulo02/LOJA DE CARROS .xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://senacspedu-my.sharepoint.com/personal/yuri_smendes_senacsp_edu_br/Documents/Capítulo02/Capítulo02/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="182" documentId="13_ncr:1_{D7366B9F-5940-410E-8B88-A4A7BBD7C952}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1C3977B6-2D3C-4F62-B833-10CF50BC1F1F}"/>
+  <xr:revisionPtr revIDLastSave="269" documentId="13_ncr:1_{D7366B9F-5940-410E-8B88-A4A7BBD7C952}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2437E38E-EE67-4093-9D1D-FBA897B79F2B}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="70">
   <si>
     <t>VENDEDOR</t>
   </si>
@@ -260,6 +260,15 @@
   </si>
   <si>
     <t>Senão "Vazio"</t>
+  </si>
+  <si>
+    <t>#=SES(F3="Ótimo";"Viagem para Natal";E(C3&lt;=$D$1;C3&gt;=100000);"Notebook";OU(C3&lt;$D$1;C3&gt;$D$1);"N/A")</t>
+  </si>
+  <si>
+    <t>FUNÇÕES / OUTRA OPÇÕES</t>
+  </si>
+  <si>
+    <t>#=CONT.SE(VENDAS!B3:B22;RELATÓRIO!D1) -  coletando informação a partir do nome do quadro</t>
   </si>
 </sst>
 </file>
@@ -270,7 +279,7 @@
     <numFmt numFmtId="164" formatCode="_(&quot;R$&quot;* #,##0.00_);_(&quot;R$&quot;* \(#,##0.00\);_(&quot;R$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="165" formatCode="&quot;R$&quot;\ #,##0.00"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -325,8 +334,14 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="13">
+  <fills count="15">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -399,6 +414,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -450,12 +477,6 @@
     <xf numFmtId="165" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -463,9 +484,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -486,14 +504,21 @@
     <xf numFmtId="0" fontId="3" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="164" fontId="3" fillId="12" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Moeda" xfId="1" builtinId="4"/>
@@ -504,6 +529,7 @@
   <colors>
     <mruColors>
       <color rgb="FFFFFF99"/>
+      <color rgb="FFFFFFCC"/>
     </mruColors>
   </colors>
   <extLst>
@@ -804,7 +830,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J82"/>
+  <dimension ref="A1:I82"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="55.42578125" style="3" customWidth="1"/>
@@ -814,50 +840,50 @@
     <col min="5" max="5" width="17.42578125" style="3" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="16.28515625" style="3" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="17.42578125" style="3" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="9.140625" style="3"/>
-    <col min="10" max="10" width="76.5703125" style="3" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="6.5703125" style="3" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="3"/>
+    <col min="8" max="8" width="9.140625" style="3"/>
+    <col min="9" max="9" width="98" style="3" customWidth="1"/>
+    <col min="10" max="10" width="6.5703125" style="3" customWidth="1"/>
+    <col min="11" max="16384" width="9.140625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="A1" s="15" t="s">
+    <row r="1" spans="1:9" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A1" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="16">
+      <c r="B1" s="14">
         <v>50000</v>
       </c>
-      <c r="C1" s="15" t="s">
+      <c r="C1" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="D1" s="16">
+      <c r="D1" s="14">
         <v>130000</v>
       </c>
     </row>
-    <row r="2" spans="1:10" s="18" customFormat="1" ht="30" x14ac:dyDescent="0.2">
-      <c r="A2" s="17" t="s">
+    <row r="2" spans="1:9" s="16" customFormat="1" ht="30" x14ac:dyDescent="0.2">
+      <c r="A2" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="17" t="s">
+      <c r="C2" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="17" t="s">
+      <c r="D2" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="17" t="s">
+      <c r="E2" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="17" t="s">
+      <c r="F2" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="G2" s="17" t="s">
+      <c r="G2" s="15" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>37</v>
       </c>
@@ -867,27 +893,27 @@
       <c r="C3" s="12">
         <v>150000</v>
       </c>
-      <c r="D3" s="36">
-        <f>_xlfn.RANK.EQ(C3,$C$3:$C$22,0)</f>
+      <c r="D3" s="33">
+        <f>IFERROR(_xlfn.RANK.EQ(C3,$C$3:$C$22,0),"")</f>
         <v>1</v>
       </c>
-      <c r="E3" s="38">
+      <c r="E3" s="34">
         <f>IF(D3=1,$B$1/RELATÓRIO!$B$10,0)</f>
         <v>25000</v>
       </c>
-      <c r="F3" s="41" t="str" cm="1">
+      <c r="F3" s="37" t="str" cm="1">
         <f t="array" ref="F3">_xlfn.IFS(D3=1,"Excelente",C3&gt;$D$1,"Ótimo",C3=$D$1,"Bom",C3&lt;$D$1,"Melhorar")</f>
         <v>Excelente</v>
       </c>
-      <c r="G3" s="13" t="str" cm="1">
-        <f t="array" ref="G3">_xlfn.IFS(F6="Ótimo","Viagem para Natal",C6&lt;=$D$1&amp;C6,AND(C6&gt;=10000,"Notebook",C3&gt;$D$1,""))</f>
-        <v>Viagem para Natal</v>
-      </c>
-      <c r="J3" s="21" t="s">
+      <c r="G3" s="42" t="str" cm="1">
+        <f t="array" ref="G3">_xlfn.IFS(F3="Ótimo","Viagem para Natal",AND(C3&lt;=$D$1,C3&gt;=100000),"Notebook",OR(C3&lt;$D$1,C3&gt;$D$1),"N/A")</f>
+        <v>N/A</v>
+      </c>
+      <c r="I3" s="18" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>38</v>
       </c>
@@ -897,27 +923,27 @@
       <c r="C4" s="12">
         <v>150000</v>
       </c>
-      <c r="D4" s="14">
-        <f>_xlfn.RANK.EQ(C4,$C$3:$C$22,0)</f>
+      <c r="D4" s="33">
+        <f t="shared" ref="D4:D22" si="0">IFERROR(_xlfn.RANK.EQ(C4,$C$3:$C$22,0),"")</f>
         <v>1</v>
       </c>
-      <c r="E4" s="37">
+      <c r="E4" s="34">
         <f>IF(D4=1,$B$1/RELATÓRIO!$B$10,0)</f>
         <v>25000</v>
       </c>
-      <c r="F4" s="1" t="str" cm="1">
+      <c r="F4" s="37" t="str" cm="1">
         <f t="array" ref="F4">_xlfn.IFS(D4=1,"Excelente",C4&gt;$D$1,"Ótimo",C4=$D$1,"Bom",C4&lt;$D$1,"Melhorar")</f>
         <v>Excelente</v>
       </c>
-      <c r="G4" s="13" t="str" cm="1">
-        <f t="array" ref="G4">_xlfn.IFS(F7="Ótimo","Viagem para Natal",C7&lt;=$D$1&amp;C7,AND(C7&gt;=10000,"Notebook",C4&gt;$D$1,""))</f>
-        <v>Viagem para Natal</v>
-      </c>
-      <c r="J4" s="44" t="s">
+      <c r="G4" s="42" t="str" cm="1">
+        <f t="array" ref="G4">_xlfn.IFS(F4="Ótimo","Viagem para Natal",AND(C4&lt;=$D$1,C4&gt;=100000),"Notebook",OR(C4&lt;$D$1,C4&gt;$D$1),"N/A")</f>
+        <v>N/A</v>
+      </c>
+      <c r="I4" s="39" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>34</v>
       </c>
@@ -927,27 +953,27 @@
       <c r="C5" s="12">
         <v>149000</v>
       </c>
-      <c r="D5" s="14">
-        <f>_xlfn.RANK.EQ(C5,$C$3:$C$22,0)</f>
+      <c r="D5" s="33">
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="E5" s="37">
+      <c r="E5" s="34">
         <f>IF(D5=1,$B$1/RELATÓRIO!$B$10,0)</f>
         <v>0</v>
       </c>
-      <c r="F5" s="1" t="str" cm="1">
+      <c r="F5" s="37" t="str" cm="1">
         <f t="array" ref="F5">_xlfn.IFS(D5=1,"Excelente",C5&gt;$D$1,"Ótimo",C5=$D$1,"Bom",C5&lt;$D$1,"Melhorar")</f>
         <v>Ótimo</v>
       </c>
-      <c r="G5" s="13" t="str" cm="1">
-        <f t="array" ref="G5">_xlfn.IFS(F8="Ótimo","Viagem para Natal",C8&lt;=$D$1&amp;C8,AND(C8&gt;=10000,"Notebook",C5&gt;$D$1,""))</f>
+      <c r="G5" s="42" t="str" cm="1">
+        <f t="array" ref="G5">_xlfn.IFS(F5="Ótimo","Viagem para Natal",AND(C5&lt;=$D$1,C5&gt;=100000),"Notebook",OR(C5&lt;$D$1,C5&gt;$D$1),"N/A")</f>
         <v>Viagem para Natal</v>
       </c>
-      <c r="J5" s="39" t="s">
+      <c r="I5" s="35" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>44</v>
       </c>
@@ -957,24 +983,24 @@
       <c r="C6" s="12">
         <v>143000</v>
       </c>
-      <c r="D6" s="14">
-        <f>_xlfn.RANK.EQ(C6,$C$3:$C$22,0)</f>
+      <c r="D6" s="33">
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="E6" s="37">
+      <c r="E6" s="34">
         <f>IF(D6=1,$B$1/RELATÓRIO!$B$10,0)</f>
         <v>0</v>
       </c>
-      <c r="F6" s="1" t="str" cm="1">
+      <c r="F6" s="37" t="str" cm="1">
         <f t="array" ref="F6">_xlfn.IFS(D6=1,"Excelente",C6&gt;$D$1,"Ótimo",C6=$D$1,"Bom",C6&lt;$D$1,"Melhorar")</f>
         <v>Ótimo</v>
       </c>
-      <c r="G6" s="13" t="str" cm="1">
-        <f t="array" ref="G6">_xlfn.IFS(F9="Ótimo","Viagem para Natal",C9&lt;=$D$1&amp;C9,AND(C9&gt;=10000,"Notebook",C6&gt;$D$1,""))</f>
+      <c r="G6" s="42" t="str" cm="1">
+        <f t="array" ref="G6">_xlfn.IFS(F6="Ótimo","Viagem para Natal",AND(C6&lt;=$D$1,C6&gt;=100000),"Notebook",OR(C6&lt;$D$1,C6&gt;$D$1),"N/A")</f>
         <v>Viagem para Natal</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="15" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>31</v>
       </c>
@@ -984,24 +1010,24 @@
       <c r="C7" s="12">
         <v>137000</v>
       </c>
-      <c r="D7" s="14">
-        <f>_xlfn.RANK.EQ(C7,$C$3:$C$22,0)</f>
+      <c r="D7" s="33">
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="E7" s="37">
+      <c r="E7" s="34">
         <f>IF(D7=1,$B$1/RELATÓRIO!$B$10,0)</f>
         <v>0</v>
       </c>
-      <c r="F7" s="1" t="str" cm="1">
+      <c r="F7" s="37" t="str" cm="1">
         <f t="array" ref="F7">_xlfn.IFS(D7=1,"Excelente",C7&gt;$D$1,"Ótimo",C7=$D$1,"Bom",C7&lt;$D$1,"Melhorar")</f>
         <v>Ótimo</v>
       </c>
-      <c r="G7" s="13" t="b" cm="1">
-        <f t="array" ref="G7">_xlfn.IFS(F10="Ótimo","Viagem para Natal",C10&lt;=$D$1&amp;C10,AND(C10&gt;=10000,"Notebook",C7&gt;$D$1,""))</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="15" x14ac:dyDescent="0.25">
+      <c r="G7" s="42" t="str" cm="1">
+        <f t="array" ref="G7">_xlfn.IFS(F7="Ótimo","Viagem para Natal",AND(C7&lt;=$D$1,C7&gt;=100000),"Notebook",OR(C7&lt;$D$1,C7&gt;$D$1),"N/A")</f>
+        <v>Viagem para Natal</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>26</v>
       </c>
@@ -1011,24 +1037,24 @@
       <c r="C8" s="12">
         <v>134600</v>
       </c>
-      <c r="D8" s="14">
-        <f>_xlfn.RANK.EQ(C8,$C$3:$C$22,0)</f>
+      <c r="D8" s="33">
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="E8" s="37">
+      <c r="E8" s="34">
         <f>IF(D8=1,$B$1/RELATÓRIO!$B$10,0)</f>
         <v>0</v>
       </c>
-      <c r="F8" s="1" t="str" cm="1">
+      <c r="F8" s="37" t="str" cm="1">
         <f t="array" ref="F8">_xlfn.IFS(D8=1,"Excelente",C8&gt;$D$1,"Ótimo",C8=$D$1,"Bom",C8&lt;$D$1,"Melhorar")</f>
         <v>Ótimo</v>
       </c>
-      <c r="G8" s="13" t="b" cm="1">
-        <f t="array" ref="G8">_xlfn.IFS(F11="Ótimo","Viagem para Natal",C11&lt;=$D$1&amp;C11,AND(C11&gt;=10000,"Notebook",C8&gt;$D$1,""))</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="15" x14ac:dyDescent="0.25">
+      <c r="G8" s="42" t="str" cm="1">
+        <f t="array" ref="G8">_xlfn.IFS(F8="Ótimo","Viagem para Natal",AND(C8&lt;=$D$1,C8&gt;=100000),"Notebook",OR(C8&lt;$D$1,C8&gt;$D$1),"N/A")</f>
+        <v>Viagem para Natal</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>35</v>
       </c>
@@ -1038,27 +1064,27 @@
       <c r="C9" s="12">
         <v>134000</v>
       </c>
-      <c r="D9" s="14">
-        <f>_xlfn.RANK.EQ(C9,$C$3:$C$22,0)</f>
+      <c r="D9" s="33">
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="E9" s="37">
+      <c r="E9" s="34">
         <f>IF(D9=1,$B$1/RELATÓRIO!$B$10,0)</f>
         <v>0</v>
       </c>
-      <c r="F9" s="1" t="str" cm="1">
+      <c r="F9" s="37" t="str" cm="1">
         <f t="array" ref="F9">_xlfn.IFS(D9=1,"Excelente",C9&gt;$D$1,"Ótimo",C9=$D$1,"Bom",C9&lt;$D$1,"Melhorar")</f>
         <v>Ótimo</v>
       </c>
-      <c r="G9" s="13" t="b" cm="1">
-        <f t="array" ref="G9">_xlfn.IFS(F12="Ótimo","Viagem para Natal",C12&lt;=$D$1&amp;C12,AND(C12&gt;=10000,"Notebook",C9&gt;$D$1,""))</f>
-        <v>1</v>
-      </c>
-      <c r="J9" s="43" t="s">
+      <c r="G9" s="42" t="str" cm="1">
+        <f t="array" ref="G9">_xlfn.IFS(F9="Ótimo","Viagem para Natal",AND(C9&lt;=$D$1,C9&gt;=100000),"Notebook",OR(C9&lt;$D$1,C9&gt;$D$1),"N/A")</f>
+        <v>Viagem para Natal</v>
+      </c>
+      <c r="I9" s="38" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="15" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>28</v>
       </c>
@@ -1068,27 +1094,27 @@
       <c r="C10" s="12">
         <v>130000</v>
       </c>
-      <c r="D10" s="14">
-        <f>_xlfn.RANK.EQ(C10,$C$3:$C$22,0)</f>
+      <c r="D10" s="33">
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="E10" s="37">
+      <c r="E10" s="34">
         <f>IF(D10=1,$B$1/RELATÓRIO!$B$10,0)</f>
         <v>0</v>
       </c>
-      <c r="F10" s="1" t="str" cm="1">
+      <c r="F10" s="37" t="str" cm="1">
         <f t="array" ref="F10">_xlfn.IFS(D10=1,"Excelente",C10&gt;$D$1,"Ótimo",C10=$D$1,"Bom",C10&lt;$D$1,"Melhorar")</f>
         <v>Bom</v>
       </c>
-      <c r="G10" s="13" t="b" cm="1">
-        <f t="array" ref="G10">_xlfn.IFS(F13="Ótimo","Viagem para Natal",C13&lt;=$D$1&amp;C13,AND(C13&gt;=10000,"Notebook",C10&gt;$D$1,""))</f>
-        <v>0</v>
-      </c>
-      <c r="J10" s="42" t="s">
+      <c r="G10" s="42" t="str" cm="1">
+        <f t="array" ref="G10">_xlfn.IFS(F10="Ótimo","Viagem para Natal",AND(C10&lt;=$D$1,C10&gt;=100000),"Notebook",OR(C10&lt;$D$1,C10&gt;$D$1),"N/A")</f>
+        <v>Notebook</v>
+      </c>
+      <c r="I10" s="43" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="15" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>36</v>
       </c>
@@ -1098,27 +1124,27 @@
       <c r="C11" s="12">
         <v>123000</v>
       </c>
-      <c r="D11" s="14">
-        <f>_xlfn.RANK.EQ(C11,$C$3:$C$22,0)</f>
+      <c r="D11" s="33">
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="E11" s="37">
+      <c r="E11" s="34">
         <f>IF(D11=1,$B$1/RELATÓRIO!$B$10,0)</f>
         <v>0</v>
       </c>
-      <c r="F11" s="1" t="str" cm="1">
+      <c r="F11" s="37" t="str" cm="1">
         <f t="array" ref="F11">_xlfn.IFS(D11=1,"Excelente",C11&gt;$D$1,"Ótimo",C11=$D$1,"Bom",C11&lt;$D$1,"Melhorar")</f>
         <v>Melhorar</v>
       </c>
-      <c r="G11" s="13" t="b" cm="1">
-        <f t="array" ref="G11">_xlfn.IFS(F14="Ótimo","Viagem para Natal",C14&lt;=$D$1&amp;C14,AND(C14&gt;=10000,"Notebook",C11&gt;$D$1,""))</f>
-        <v>0</v>
-      </c>
-      <c r="J11" s="42" t="s">
+      <c r="G11" s="42" t="str" cm="1">
+        <f t="array" ref="G11">_xlfn.IFS(F11="Ótimo","Viagem para Natal",AND(C11&lt;=$D$1,C11&gt;=100000),"Notebook",OR(C11&lt;$D$1,C11&gt;$D$1),"N/A")</f>
+        <v>Notebook</v>
+      </c>
+      <c r="I11" s="43" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="15" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>42</v>
       </c>
@@ -1128,27 +1154,27 @@
       <c r="C12" s="12">
         <v>123000</v>
       </c>
-      <c r="D12" s="14">
-        <f>_xlfn.RANK.EQ(C12,$C$3:$C$22,0)</f>
+      <c r="D12" s="33">
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="E12" s="37">
+      <c r="E12" s="34">
         <f>IF(D12=1,$B$1/RELATÓRIO!$B$10,0)</f>
         <v>0</v>
       </c>
-      <c r="F12" s="1" t="str" cm="1">
+      <c r="F12" s="37" t="str" cm="1">
         <f t="array" ref="F12">_xlfn.IFS(D12=1,"Excelente",C12&gt;$D$1,"Ótimo",C12=$D$1,"Bom",C12&lt;$D$1,"Melhorar")</f>
         <v>Melhorar</v>
       </c>
-      <c r="G12" s="13" t="b" cm="1">
-        <f t="array" ref="G12">_xlfn.IFS(F15="Ótimo","Viagem para Natal",C15&lt;=$D$1&amp;C15,AND(C15&gt;=10000,"Notebook",C12&gt;$D$1,""))</f>
-        <v>0</v>
-      </c>
-      <c r="J12" s="42" t="s">
+      <c r="G12" s="42" t="str" cm="1">
+        <f t="array" ref="G12">_xlfn.IFS(F12="Ótimo","Viagem para Natal",AND(C12&lt;=$D$1,C12&gt;=100000),"Notebook",OR(C12&lt;$D$1,C12&gt;$D$1),"N/A")</f>
+        <v>Notebook</v>
+      </c>
+      <c r="I12" s="43" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="15" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>40</v>
       </c>
@@ -1158,27 +1184,27 @@
       <c r="C13" s="12">
         <v>120000</v>
       </c>
-      <c r="D13" s="14">
-        <f>_xlfn.RANK.EQ(C13,$C$3:$C$22,0)</f>
+      <c r="D13" s="33">
+        <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="E13" s="37">
+      <c r="E13" s="34">
         <f>IF(D13=1,$B$1/RELATÓRIO!$B$10,0)</f>
         <v>0</v>
       </c>
-      <c r="F13" s="1" t="str" cm="1">
+      <c r="F13" s="37" t="str" cm="1">
         <f t="array" ref="F13">_xlfn.IFS(D13=1,"Excelente",C13&gt;$D$1,"Ótimo",C13=$D$1,"Bom",C13&lt;$D$1,"Melhorar")</f>
         <v>Melhorar</v>
       </c>
-      <c r="G13" s="13" t="b" cm="1">
-        <f t="array" ref="G13">_xlfn.IFS(F16="Ótimo","Viagem para Natal",C16&lt;=$D$1&amp;C16,AND(C16&gt;=10000,"Notebook",C13&gt;$D$1,""))</f>
-        <v>0</v>
-      </c>
-      <c r="J13" s="42" t="s">
+      <c r="G13" s="42" t="str" cm="1">
+        <f t="array" ref="G13">_xlfn.IFS(F13="Ótimo","Viagem para Natal",AND(C13&lt;=$D$1,C13&gt;=100000),"Notebook",OR(C13&lt;$D$1,C13&gt;$D$1),"N/A")</f>
+        <v>Notebook</v>
+      </c>
+      <c r="I13" s="43" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="15" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>25</v>
       </c>
@@ -1188,27 +1214,27 @@
       <c r="C14" s="12">
         <v>100000</v>
       </c>
-      <c r="D14" s="14">
-        <f>_xlfn.RANK.EQ(C14,$C$3:$C$22,0)</f>
+      <c r="D14" s="33">
+        <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="E14" s="37">
+      <c r="E14" s="34">
         <f>IF(D14=1,$B$1/RELATÓRIO!$B$10,0)</f>
         <v>0</v>
       </c>
-      <c r="F14" s="1" t="str" cm="1">
+      <c r="F14" s="37" t="str" cm="1">
         <f t="array" ref="F14">_xlfn.IFS(D14=1,"Excelente",C14&gt;$D$1,"Ótimo",C14=$D$1,"Bom",C14&lt;$D$1,"Melhorar")</f>
         <v>Melhorar</v>
       </c>
-      <c r="G14" s="13" t="b" cm="1">
-        <f t="array" ref="G14">_xlfn.IFS(F17="Ótimo","Viagem para Natal",C17&lt;=$D$1&amp;C17,AND(C17&gt;=10000,"Notebook",C14&gt;$D$1,""))</f>
-        <v>0</v>
-      </c>
-      <c r="J14" s="42" t="s">
+      <c r="G14" s="42" t="str" cm="1">
+        <f t="array" ref="G14">_xlfn.IFS(F14="Ótimo","Viagem para Natal",AND(C14&lt;=$D$1,C14&gt;=100000),"Notebook",OR(C14&lt;$D$1,C14&gt;$D$1),"N/A")</f>
+        <v>Notebook</v>
+      </c>
+      <c r="I14" s="43" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="15" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>29</v>
       </c>
@@ -1218,25 +1244,25 @@
       <c r="C15" s="12">
         <v>90870</v>
       </c>
-      <c r="D15" s="14">
-        <f>_xlfn.RANK.EQ(C15,$C$3:$C$22,0)</f>
+      <c r="D15" s="33">
+        <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="E15" s="37">
+      <c r="E15" s="34">
         <f>IF(D15=1,$B$1/RELATÓRIO!$B$10,0)</f>
         <v>0</v>
       </c>
-      <c r="F15" s="1" t="str" cm="1">
+      <c r="F15" s="37" t="str" cm="1">
         <f t="array" ref="F15">_xlfn.IFS(D15=1,"Excelente",C15&gt;$D$1,"Ótimo",C15=$D$1,"Bom",C15&lt;$D$1,"Melhorar")</f>
         <v>Melhorar</v>
       </c>
-      <c r="G15" s="13" t="b" cm="1">
-        <f t="array" ref="G15">_xlfn.IFS(F18="Ótimo","Viagem para Natal",C18&lt;=$D$1&amp;C18,AND(C18&gt;=10000,"Notebook",C15&gt;$D$1,""))</f>
-        <v>0</v>
-      </c>
-      <c r="J15" s="40"/>
-    </row>
-    <row r="16" spans="1:10" ht="15" x14ac:dyDescent="0.25">
+      <c r="G15" s="42" t="str" cm="1">
+        <f t="array" ref="G15">_xlfn.IFS(F15="Ótimo","Viagem para Natal",AND(C15&lt;=$D$1,C15&gt;=100000),"Notebook",OR(C15&lt;$D$1,C15&gt;$D$1),"N/A")</f>
+        <v>N/A</v>
+      </c>
+      <c r="I15" s="36"/>
+    </row>
+    <row r="16" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>41</v>
       </c>
@@ -1246,25 +1272,25 @@
       <c r="C16" s="12">
         <v>87900</v>
       </c>
-      <c r="D16" s="14">
-        <f>_xlfn.RANK.EQ(C16,$C$3:$C$22,0)</f>
+      <c r="D16" s="33">
+        <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="E16" s="37">
+      <c r="E16" s="34">
         <f>IF(D16=1,$B$1/RELATÓRIO!$B$10,0)</f>
         <v>0</v>
       </c>
-      <c r="F16" s="1" t="str" cm="1">
+      <c r="F16" s="37" t="str" cm="1">
         <f t="array" ref="F16">_xlfn.IFS(D16=1,"Excelente",C16&gt;$D$1,"Ótimo",C16=$D$1,"Bom",C16&lt;$D$1,"Melhorar")</f>
         <v>Melhorar</v>
       </c>
-      <c r="G16" s="13" t="b" cm="1">
-        <f t="array" ref="G16">_xlfn.IFS(F19="Ótimo","Viagem para Natal",C19&lt;=$D$1&amp;C19,AND(C19&gt;=10000,"Notebook",C16&gt;$D$1,""))</f>
-        <v>0</v>
-      </c>
-      <c r="J16" s="40"/>
-    </row>
-    <row r="17" spans="1:10" ht="15" x14ac:dyDescent="0.25">
+      <c r="G16" s="42" t="str" cm="1">
+        <f t="array" ref="G16">_xlfn.IFS(F16="Ótimo","Viagem para Natal",AND(C16&lt;=$D$1,C16&gt;=100000),"Notebook",OR(C16&lt;$D$1,C16&gt;$D$1),"N/A")</f>
+        <v>N/A</v>
+      </c>
+      <c r="I16" s="36"/>
+    </row>
+    <row r="17" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>43</v>
       </c>
@@ -1274,27 +1300,27 @@
       <c r="C17" s="12">
         <v>76900</v>
       </c>
-      <c r="D17" s="14">
-        <f>_xlfn.RANK.EQ(C17,$C$3:$C$22,0)</f>
+      <c r="D17" s="33">
+        <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="E17" s="37">
+      <c r="E17" s="34">
         <f>IF(D17=1,$B$1/RELATÓRIO!$B$10,0)</f>
         <v>0</v>
       </c>
-      <c r="F17" s="1" t="str" cm="1">
+      <c r="F17" s="37" t="str" cm="1">
         <f t="array" ref="F17">_xlfn.IFS(D17=1,"Excelente",C17&gt;$D$1,"Ótimo",C17=$D$1,"Bom",C17&lt;$D$1,"Melhorar")</f>
         <v>Melhorar</v>
       </c>
-      <c r="G17" s="13" t="b" cm="1">
-        <f t="array" ref="G17">_xlfn.IFS(F20="Ótimo","Viagem para Natal",C20&lt;=$D$1&amp;C20,AND(C20&gt;=10000,"Notebook",C17&gt;$D$1,""))</f>
-        <v>0</v>
-      </c>
-      <c r="J17" s="43" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" ht="15" x14ac:dyDescent="0.25">
+      <c r="G17" s="42" t="str" cm="1">
+        <f t="array" ref="G17">_xlfn.IFS(F17="Ótimo","Viagem para Natal",AND(C17&lt;=$D$1,C17&gt;=100000),"Notebook",OR(C17&lt;$D$1,C17&gt;$D$1),"N/A")</f>
+        <v>N/A</v>
+      </c>
+      <c r="I17" s="41" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>32</v>
       </c>
@@ -1304,27 +1330,27 @@
       <c r="C18" s="12">
         <v>67800</v>
       </c>
-      <c r="D18" s="14">
-        <f>_xlfn.RANK.EQ(C18,$C$3:$C$22,0)</f>
+      <c r="D18" s="33">
+        <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="E18" s="37">
+      <c r="E18" s="34">
         <f>IF(D18=1,$B$1/RELATÓRIO!$B$10,0)</f>
         <v>0</v>
       </c>
-      <c r="F18" s="1" t="str" cm="1">
+      <c r="F18" s="37" t="str" cm="1">
         <f t="array" ref="F18">_xlfn.IFS(D18=1,"Excelente",C18&gt;$D$1,"Ótimo",C18=$D$1,"Bom",C18&lt;$D$1,"Melhorar")</f>
         <v>Melhorar</v>
       </c>
-      <c r="G18" s="13" t="b" cm="1">
-        <f t="array" ref="G18">_xlfn.IFS(F21="Ótimo","Viagem para Natal",C21&lt;=$D$1&amp;C21,AND(C21&gt;=10000,"Notebook",C18&gt;$D$1,""))</f>
-        <v>0</v>
-      </c>
-      <c r="J18" s="42" t="s">
+      <c r="G18" s="42" t="str" cm="1">
+        <f t="array" ref="G18">_xlfn.IFS(F18="Ótimo","Viagem para Natal",AND(C18&lt;=$D$1,C18&gt;=100000),"Notebook",OR(C18&lt;$D$1,C18&gt;$D$1),"N/A")</f>
+        <v>N/A</v>
+      </c>
+      <c r="I18" s="43" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="15" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>27</v>
       </c>
@@ -1334,27 +1360,27 @@
       <c r="C19" s="12">
         <v>50000</v>
       </c>
-      <c r="D19" s="14">
-        <f>_xlfn.RANK.EQ(C19,$C$3:$C$22,0)</f>
+      <c r="D19" s="33">
+        <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="E19" s="37">
+      <c r="E19" s="34">
         <f>IF(D19=1,$B$1/RELATÓRIO!$B$10,0)</f>
         <v>0</v>
       </c>
-      <c r="F19" s="1" t="str" cm="1">
+      <c r="F19" s="37" t="str" cm="1">
         <f t="array" ref="F19">_xlfn.IFS(D19=1,"Excelente",C19&gt;$D$1,"Ótimo",C19=$D$1,"Bom",C19&lt;$D$1,"Melhorar")</f>
         <v>Melhorar</v>
       </c>
-      <c r="G19" s="13" t="e" cm="1">
-        <f t="array" ref="G19">_xlfn.IFS(F22="Ótimo","Viagem para Natal",C22&lt;=$D$1&amp;C22,AND(C22&gt;=10000,"Notebook",C19&gt;$D$1,""))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="J19" s="42" t="s">
+      <c r="G19" s="42" t="str" cm="1">
+        <f t="array" ref="G19">_xlfn.IFS(F19="Ótimo","Viagem para Natal",AND(C19&lt;=$D$1,C19&gt;=100000),"Notebook",OR(C19&lt;$D$1,C19&gt;$D$1),"N/A")</f>
+        <v>N/A</v>
+      </c>
+      <c r="I19" s="43" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="15" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>30</v>
       </c>
@@ -1364,27 +1390,27 @@
       <c r="C20" s="12">
         <v>45000</v>
       </c>
-      <c r="D20" s="14">
-        <f>_xlfn.RANK.EQ(C20,$C$3:$C$22,0)</f>
+      <c r="D20" s="33">
+        <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="E20" s="37">
+      <c r="E20" s="34">
         <f>IF(D20=1,$B$1/RELATÓRIO!$B$10,0)</f>
         <v>0</v>
       </c>
-      <c r="F20" s="1" t="str" cm="1">
+      <c r="F20" s="37" t="str" cm="1">
         <f t="array" ref="F20">_xlfn.IFS(D20=1,"Excelente",C20&gt;$D$1,"Ótimo",C20=$D$1,"Bom",C20&lt;$D$1,"Melhorar")</f>
         <v>Melhorar</v>
       </c>
-      <c r="G20" s="13" t="b" cm="1">
-        <f t="array" ref="G20">_xlfn.IFS(F23="Ótimo","Viagem para Natal",C23&lt;=$D$1&amp;C23,AND(C23&gt;=10000,"Notebook",C20&gt;$D$1,""))</f>
-        <v>0</v>
-      </c>
-      <c r="J20" s="42" t="s">
+      <c r="G20" s="42" t="str" cm="1">
+        <f t="array" ref="G20">_xlfn.IFS(F20="Ótimo","Viagem para Natal",AND(C20&lt;=$D$1,C20&gt;=100000),"Notebook",OR(C20&lt;$D$1,C20&gt;$D$1),"N/A")</f>
+        <v>N/A</v>
+      </c>
+      <c r="I20" s="43" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="15" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>33</v>
       </c>
@@ -1394,27 +1420,27 @@
       <c r="C21" s="12">
         <v>23000</v>
       </c>
-      <c r="D21" s="14">
-        <f>_xlfn.RANK.EQ(C21,$C$3:$C$22,0)</f>
+      <c r="D21" s="33">
+        <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="E21" s="37">
+      <c r="E21" s="34">
         <f>IF(D21=1,$B$1/RELATÓRIO!$B$10,0)</f>
         <v>0</v>
       </c>
-      <c r="F21" s="1" t="str" cm="1">
+      <c r="F21" s="37" t="str" cm="1">
         <f t="array" ref="F21">_xlfn.IFS(D21=1,"Excelente",C21&gt;$D$1,"Ótimo",C21=$D$1,"Bom",C21&lt;$D$1,"Melhorar")</f>
         <v>Melhorar</v>
       </c>
-      <c r="G21" s="13" t="b" cm="1">
-        <f t="array" ref="G21">_xlfn.IFS(F24="Ótimo","Viagem para Natal",C24&lt;=$D$1&amp;C24,AND(C24&gt;=10000,"Notebook",C21&gt;$D$1,""))</f>
-        <v>0</v>
-      </c>
-      <c r="J21" s="42" t="s">
+      <c r="G21" s="42" t="str" cm="1">
+        <f t="array" ref="G21">_xlfn.IFS(F21="Ótimo","Viagem para Natal",AND(C21&lt;=$D$1,C21&gt;=100000),"Notebook",OR(C21&lt;$D$1,C21&gt;$D$1),"N/A")</f>
+        <v>N/A</v>
+      </c>
+      <c r="I21" s="43" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="22" spans="1:10" ht="15" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>39</v>
       </c>
@@ -1422,53 +1448,54 @@
         <v>24</v>
       </c>
       <c r="C22" s="12"/>
-      <c r="D22" s="14" t="e">
-        <f>_xlfn.RANK.EQ(C22,$C$3:$C$22,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="E22" s="37" t="e">
+      <c r="D22" s="33" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E22" s="34">
         <f>IF(D22=1,$B$1/RELATÓRIO!$B$10,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F22" s="1" t="e" cm="1">
+        <v>0</v>
+      </c>
+      <c r="F22" s="37" t="str" cm="1">
         <f t="array" ref="F22">_xlfn.IFS(D22=1,"Excelente",C22&gt;$D$1,"Ótimo",C22=$D$1,"Bom",C22&lt;$D$1,"Melhorar")</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G22" s="13" t="b" cm="1">
-        <f t="array" ref="G22">_xlfn.IFS(F25="Ótimo","Viagem para Natal",C25&lt;=$D$1&amp;C25,AND(C25&gt;=10000,"Notebook",C22&gt;$D$1,""))</f>
-        <v>0</v>
-      </c>
-      <c r="J22" s="42"/>
-    </row>
-    <row r="24" spans="1:10" ht="15" x14ac:dyDescent="0.25">
+        <v>Melhorar</v>
+      </c>
+      <c r="G22" s="42" t="str" cm="1">
+        <f t="array" ref="G22">_xlfn.IFS(F22="Ótimo","Viagem para Natal",AND(C22&lt;=$D$1,C22&gt;=100000),"Notebook",OR(C22&lt;$D$1,C22&gt;$D$1),"N/A")</f>
+        <v>N/A</v>
+      </c>
+      <c r="I22" s="43"/>
+    </row>
+    <row r="24" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A24" s="4"/>
     </row>
-    <row r="25" spans="1:10" ht="15" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A25" s="4"/>
-    </row>
-    <row r="26" spans="1:10" ht="15" x14ac:dyDescent="0.25">
+      <c r="I25" s="44"/>
+    </row>
+    <row r="26" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A26" s="4"/>
     </row>
-    <row r="27" spans="1:10" ht="15" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A27" s="4"/>
     </row>
-    <row r="28" spans="1:10" ht="15" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A28" s="4"/>
       <c r="B28" s="4"/>
     </row>
-    <row r="29" spans="1:10" ht="15" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A29" s="4"/>
       <c r="B29" s="4"/>
     </row>
-    <row r="30" spans="1:10" ht="15" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A30" s="4"/>
       <c r="B30" s="4"/>
     </row>
-    <row r="31" spans="1:10" ht="15" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A31" s="4"/>
       <c r="B31" s="4"/>
     </row>
-    <row r="32" spans="1:10" ht="15" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A32" s="4"/>
       <c r="B32" s="4"/>
     </row>
@@ -1834,15 +1861,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="40" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="D1" s="20" t="s">
+      <c r="B1" s="40"/>
+      <c r="D1" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="E1" s="20"/>
-      <c r="G1" s="19" t="s">
+      <c r="E1" s="40"/>
+      <c r="G1" s="17" t="s">
         <v>45</v>
       </c>
     </row>
@@ -1850,7 +1877,7 @@
       <c r="A2" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="23">
+      <c r="B2" s="20">
         <f>MAX(VENDAS!C3:C22)</f>
         <v>150000</v>
       </c>
@@ -1858,10 +1885,10 @@
         <v>15</v>
       </c>
       <c r="E2" s="9">
-        <f>COUNTIF(VENDAS!B3:B22,"usados")</f>
+        <f>COUNTIF(VENDAS!B3:B22,RELATÓRIO!D1)</f>
         <v>8</v>
       </c>
-      <c r="G2" s="22" t="s">
+      <c r="G2" s="19" t="s">
         <v>46</v>
       </c>
     </row>
@@ -1869,7 +1896,7 @@
       <c r="A3" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="25">
+      <c r="B3" s="22">
         <f>MIN(VENDAS!C3:C22)</f>
         <v>23000</v>
       </c>
@@ -1880,7 +1907,7 @@
         <f>COUNTIFS(VENDAS!B3:B22,"USADOS",VENDAS!C3:C22,LARGE(VENDAS!D1,1))</f>
         <v>0</v>
       </c>
-      <c r="G3" s="24" t="s">
+      <c r="G3" s="21" t="s">
         <v>47</v>
       </c>
     </row>
@@ -1888,7 +1915,7 @@
       <c r="A4" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="27">
+      <c r="B4" s="24">
         <f>AVERAGE(VENDAS!C3:C21)</f>
         <v>107108.94736842105</v>
       </c>
@@ -1899,7 +1926,7 @@
         <f>AVERAGEIF(VENDAS!B3:B22,"usados",VENDAS!C3:C22)</f>
         <v>101587.5</v>
       </c>
-      <c r="G4" s="26" t="s">
+      <c r="G4" s="23" t="s">
         <v>48</v>
       </c>
     </row>
@@ -1911,16 +1938,16 @@
         <f>AVERAGEIFS(VENDAS!C3:C22,VENDAS!B3:B22,"usados",VENDAS!E3:E22,"=0")</f>
         <v>101587.5</v>
       </c>
-      <c r="G5" s="28" t="s">
+      <c r="G5" s="25" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="20" t="s">
+      <c r="A6" s="40" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="20"/>
-      <c r="G6" s="31" t="s">
+      <c r="B6" s="40"/>
+      <c r="G6" s="28" t="s">
         <v>50</v>
       </c>
     </row>
@@ -1928,15 +1955,15 @@
       <c r="A7" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="29">
+      <c r="B7" s="26">
         <f>COUNTA(VENDAS!A3:A22)</f>
         <v>20</v>
       </c>
-      <c r="D7" s="20" t="s">
+      <c r="D7" s="40" t="s">
         <v>23</v>
       </c>
-      <c r="E7" s="20"/>
-      <c r="G7" s="32" t="s">
+      <c r="E7" s="40"/>
+      <c r="G7" s="29" t="s">
         <v>51</v>
       </c>
     </row>
@@ -1944,7 +1971,7 @@
       <c r="A8" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="30">
+      <c r="B8" s="27">
         <f>COUNTBLANK(VENDAS!C3:C22)</f>
         <v>1</v>
       </c>
@@ -1952,10 +1979,10 @@
         <v>15</v>
       </c>
       <c r="E8" s="9">
-        <f>COUNTIF(VENDAS!B3:B22,"zero km")</f>
+        <f>COUNTIF(VENDAS!B3:B22,RELATÓRIO!D7)</f>
         <v>7</v>
       </c>
-      <c r="G8" s="35" t="s">
+      <c r="G8" s="32" t="s">
         <v>52</v>
       </c>
     </row>
@@ -1963,7 +1990,7 @@
       <c r="A9" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="34">
+      <c r="B9" s="31">
         <f>COUNT(VENDAS!C3:C22)</f>
         <v>19</v>
       </c>
@@ -1982,7 +2009,7 @@
       <c r="A10" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="33">
+      <c r="B10" s="30">
         <f>COUNTIF(VENDAS!C3:C21,MAX(RELATÓRIO!B2))</f>
         <v>2</v>
       </c>
@@ -2006,18 +2033,26 @@
         <v>119228.33333333333</v>
       </c>
     </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G12" s="17" t="s">
+        <v>68</v>
+      </c>
+    </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="D13" s="20" t="s">
+      <c r="D13" s="40" t="s">
         <v>24</v>
       </c>
-      <c r="E13" s="20"/>
+      <c r="E13" s="40"/>
+      <c r="G13" s="8" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D14" s="9" t="s">
         <v>15</v>
       </c>
       <c r="E14" s="9">
-        <f>COUNTIF(VENDAS!B3:B22,"isenções")</f>
+        <f>COUNTIF(VENDAS!B3:B22,RELATÓRIO!D13)</f>
         <v>5</v>
       </c>
     </row>
@@ -2061,21 +2096,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100CEB2B541769F8A4991DE642272C524BB" ma:contentTypeVersion="0" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="7ae862ae5010eca0394e8ac9f072291e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="397561fba88d9dece65508bac662637b">
     <xsd:element name="properties">
@@ -2189,10 +2209,33 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CDE8DEAC-3A9C-404A-8264-9223756F60BA}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C4065620-52E6-42F5-9F09-6EBAD10A2948}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -2207,17 +2250,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C4065620-52E6-42F5-9F09-6EBAD10A2948}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CDE8DEAC-3A9C-404A-8264-9223756F60BA}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>